--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_FUNDACIÓ CAIXA RURAL VILA-REAL.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_FUNDACIÓ CAIXA RURAL VILA-REAL.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>8.463200000000001</v>
+        <v>8.432499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.126</v>
+        <v>6.8326</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3372</v>
+        <v>1.5999</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0918</v>
+        <v>4.0456</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9913</v>
+        <v>-1.1501</v>
       </c>
       <c r="I2" t="n">
-        <v>5.083</v>
+        <v>5.1957</v>
       </c>
       <c r="J2" t="n">
-        <v>6.417400000000001</v>
+        <v>6.7913</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7247</v>
+        <v>2.8918</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6928</v>
+        <v>3.8995</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.3257</v>
+        <v>-2.7457</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.7159</v>
+        <v>-4.0419</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3903</v>
+        <v>1.2962</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.4016</v>
+        <v>-5.2578</v>
       </c>
       <c r="R2" t="n">
-        <v>3.401</v>
+        <v>3.3105</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7726</v>
+        <v>2.6711</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8117000000000001</v>
+        <v>0.8492000000000002</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9609</v>
+        <v>1.822</v>
       </c>
       <c r="V2" t="n">
-        <v>3.5993</v>
+        <v>3.6632</v>
       </c>
       <c r="W2" t="n">
-        <v>4.2984</v>
+        <v>4.4501</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6990999999999999</v>
+        <v>-0.7868999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -643,31 +643,31 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1991</v>
+        <v>4.2869</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1991</v>
+        <v>4.2869</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1991</v>
+        <v>4.2869</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3994</v>
+        <v>2.4632</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7997</v>
+        <v>1.8237</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1991</v>
+        <v>4.2869</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3994</v>
+        <v>2.4632</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7997</v>
+        <v>1.8237</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.897</v>
+        <v>3.8865</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3064</v>
+        <v>4.5424</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4094</v>
+        <v>-0.6559</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4377</v>
+        <v>1.4556</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4131</v>
+        <v>2.4395</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9755</v>
+        <v>-0.984</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9684</v>
+        <v>3.1843</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1207</v>
+        <v>4.2618</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1522</v>
+        <v>-1.0775</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5307</v>
+        <v>-1.7287</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7074</v>
+        <v>-1.8223</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1767</v>
+        <v>0.09360000000000002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8003</v>
+        <v>0.7789</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8003</v>
+        <v>0.7789</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0593</v>
+        <v>1.0415</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7382000000000001</v>
+        <v>0.7475999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3211</v>
+        <v>0.2939</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2883</v>
+        <v>3.1202</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5124</v>
+        <v>4.8233</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.224</v>
+        <v>-1.7031</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1896999999999998</v>
+        <v>0.1286999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.9417</v>
+        <v>-2.9948</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1313</v>
+        <v>3.1235</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3705</v>
+        <v>3.5956</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009100000000000108</v>
+        <v>0.1669</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3614</v>
+        <v>3.4286</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.1808</v>
+        <v>-3.4668</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.9507</v>
+        <v>-3.1617</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2301</v>
+        <v>-0.3051</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0009</v>
+        <v>2.9211</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0779</v>
+        <v>1.0509</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4229</v>
+        <v>1.4213</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.345</v>
+        <v>-0.3703</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4204000000000001</v>
+        <v>0.3826</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1195</v>
+        <v>1.1695</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6990999999999999</v>
+        <v>-0.7869</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2813</v>
+        <v>1.3149</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1335999999999999</v>
+        <v>0.1055999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4148</v>
+        <v>1.2093</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4778</v>
+        <v>2.4808</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3894</v>
+        <v>0.3555</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0885</v>
+        <v>2.1253</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2869</v>
+        <v>2.4372</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8833</v>
+        <v>0.9699</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4036</v>
+        <v>1.4673</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1908</v>
+        <v>0.04350000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.494</v>
+        <v>-0.6144000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6849000000000001</v>
+        <v>0.6578999999999999</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0005</v>
+        <v>1.9473</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5163</v>
+        <v>-0.5038</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2603</v>
+        <v>0.2779</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7766</v>
+        <v>-0.7817000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8026</v>
+        <v>0.7639</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1214</v>
+        <v>1.1913</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3188</v>
+        <v>-0.4274</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7931</v>
+        <v>0.8097</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1022</v>
+        <v>-1.1063</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8953</v>
+        <v>1.9161</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2436</v>
+        <v>1.3057</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.638</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8816</v>
+        <v>1.9292</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4505</v>
+        <v>-0.496</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4642</v>
+        <v>-0.4829</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1289</v>
+        <v>0.1237</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1222</v>
+        <v>-0.1144</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2511</v>
+        <v>0.2381</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1033,22 +1033,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1549</v>
+        <v>0.1515</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1549</v>
+        <v>0.1515</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1060,13 +1060,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1163</v>
+        <v>-0.1144</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1163</v>
+        <v>-0.1144</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4077000000000001</v>
+        <v>-0.5922999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.06980000000000008</v>
+        <v>0.2274</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3379000000000003</v>
+        <v>-0.8197000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.6905</v>
+        <v>-4.7646</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.734299999999999</v>
+        <v>-4.8539</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04380000000000001</v>
+        <v>0.08940000000000003</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2591</v>
+        <v>-2.0122</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1906</v>
+        <v>-1.0646</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0684</v>
+        <v>-0.9476</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4315</v>
+        <v>-2.7524</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.5436</v>
+        <v>-3.7894</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1123</v>
+        <v>1.0369</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9624</v>
+        <v>2.887</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8698</v>
+        <v>1.8754</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0927</v>
+        <v>1.0116</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6466000000000001</v>
+        <v>-0.6269</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3971</v>
+        <v>-2.255</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7505</v>
+        <v>1.628</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6181</v>
+        <v>0.6003000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8249</v>
+        <v>0.7964</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2068</v>
+        <v>-0.1961</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4944</v>
+        <v>-0.4156</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6616</v>
+        <v>0.7108000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.156</v>
+        <v>-1.1264</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1124</v>
+        <v>1.0159</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1632</v>
+        <v>0.08560000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9492</v>
+        <v>0.9303</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2000999999999999</v>
+        <v>0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2004</v>
+        <v>1.1684</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4646</v>
+        <v>-1.422</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9024</v>
+        <v>-0.8657</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5622</v>
+        <v>-0.5563</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8649000000000002</v>
+        <v>-0.7258</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4139</v>
+        <v>1.366</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4510000000000001</v>
+        <v>-2.0918</v>
       </c>
       <c r="G11" t="n">
-        <v>4.1582</v>
+        <v>0.472</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4807</v>
+        <v>-1.5513</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6776</v>
+        <v>2.0234</v>
       </c>
       <c r="J11" t="n">
-        <v>4.190300000000001</v>
+        <v>3.3232</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6249</v>
+        <v>1.3933</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5653</v>
+        <v>1.9298</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.03210000000000002</v>
+        <v>-2.8511</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1444</v>
+        <v>-2.9447</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1122</v>
+        <v>0.09350000000000003</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.0009</v>
+        <v>-3.1158</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.2015</v>
+        <v>-5.0632</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2006</v>
+        <v>1.9474</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0373</v>
+        <v>-0.8036</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8623</v>
+        <v>-0.226</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8995</v>
+        <v>-0.5775</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.0595</v>
+        <v>2.7216</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4596</v>
+        <v>3.3321</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.519</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9063000000000001</v>
+        <v>-0.8726</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8319000000000001</v>
+        <v>0.05690000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7382</v>
+        <v>-0.9296</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4552</v>
+        <v>4.1406</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4927</v>
+        <v>0.4366</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9479</v>
+        <v>3.704</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0362</v>
+        <v>4.4298</v>
       </c>
       <c r="K12" t="n">
-        <v>1.265</v>
+        <v>1.7628</v>
       </c>
       <c r="L12" t="n">
-        <v>1.7712</v>
+        <v>2.667</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.581</v>
+        <v>-0.2892</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.7577</v>
+        <v>-1.3262</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1768</v>
+        <v>1.037</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.2009</v>
+        <v>-2.9211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.201499999999999</v>
+        <v>-5.0631</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0006</v>
+        <v>2.1421</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8200000000000001</v>
+        <v>0.01889999999999997</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2621</v>
+        <v>-0.8103</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>2.6593</v>
+        <v>-2.111</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2592</v>
+        <v>1.5005</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5999</v>
+        <v>-3.6116</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7225</v>
+        <v>-1.7125</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5427</v>
+        <v>-0.3185</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1798</v>
+        <v>-1.394</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08660000000000001</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8721000000000001</v>
+        <v>-0.971</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9587</v>
+        <v>1.0526</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7531</v>
+        <v>0.9274000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4999</v>
+        <v>0.5132</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2532</v>
+        <v>0.4142</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6665000000000001</v>
+        <v>-0.8459000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.372</v>
+        <v>-1.4842</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7054999999999999</v>
+        <v>0.6382</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0003</v>
+        <v>0.9736</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5496</v>
+        <v>-2.4882</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0958</v>
+        <v>-1.0511</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4538</v>
+        <v>-1.437</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.6495</v>
+        <v>-3.5586</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.4015</v>
+        <v>-2.0121</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2481</v>
+        <v>-1.5465</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.8351</v>
+        <v>-1.8782</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.7735</v>
+        <v>-3.7793</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9384</v>
+        <v>1.9011</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2309</v>
+        <v>1.415</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9306999999999999</v>
+        <v>-0.7978</v>
       </c>
       <c r="L14" t="n">
-        <v>2.1616</v>
+        <v>2.2129</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.066</v>
+        <v>-3.2932</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.8428</v>
+        <v>-2.9816</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2232</v>
+        <v>-0.3117</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.601900000000001</v>
+        <v>-6.4263</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.0023</v>
+        <v>-7.789400000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4004</v>
+        <v>1.3631</v>
       </c>
       <c r="S14" t="n">
-        <v>5.2882</v>
+        <v>5.180099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.8706</v>
+        <v>4.7965</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4176</v>
+        <v>0.3836</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5007</v>
+        <v>-0.4342</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.5007</v>
+        <v>-0.4342</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.7063</v>
+        <v>-4.7211</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.0351</v>
+        <v>-3.6761</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6710999999999998</v>
+        <v>-1.0451</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.54</v>
+        <v>-0.5457999999999998</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5272</v>
+        <v>-1.4921</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9873000000000001</v>
+        <v>0.9464000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1652999999999998</v>
+        <v>0.06450000000000022</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1691</v>
+        <v>0.01560000000000006</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003799999999999915</v>
+        <v>0.04890000000000005</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3747</v>
+        <v>-0.6103</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3581</v>
+        <v>-1.5078</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9835</v>
+        <v>0.8975</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.2007</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.401</v>
+        <v>-3.3105</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2464</v>
+        <v>-0.2532</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4688</v>
+        <v>-0.4301</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2225</v>
+        <v>0.1768</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>9.182600000000001</v>
+        <v>9.146600000000005</v>
       </c>
       <c r="E16" t="n">
-        <v>11.1035</v>
+        <v>15.1707</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9209</v>
+        <v>-6.0244</v>
       </c>
       <c r="G16" t="n">
-        <v>11.7129</v>
+        <v>11.579</v>
       </c>
       <c r="H16" t="n">
-        <v>-10.9275</v>
+        <v>-11.4076</v>
       </c>
       <c r="I16" t="n">
-        <v>22.6404</v>
+        <v>22.9869</v>
       </c>
       <c r="J16" t="n">
-        <v>26.7776</v>
+        <v>29.33309999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>11.2602</v>
+        <v>12.6634</v>
       </c>
       <c r="L16" t="n">
-        <v>15.5176</v>
+        <v>16.6696</v>
       </c>
       <c r="M16" t="n">
-        <v>-15.0651</v>
+        <v>-17.7541</v>
       </c>
       <c r="N16" t="n">
-        <v>-22.1876</v>
+        <v>-24.0715</v>
       </c>
       <c r="O16" t="n">
-        <v>7.122999999999999</v>
+        <v>6.316999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-11.0031</v>
+        <v>-10.7107</v>
       </c>
       <c r="Q16" t="n">
-        <v>-32.0094</v>
+        <v>-31.1577</v>
       </c>
       <c r="R16" t="n">
-        <v>21.006</v>
+        <v>20.4472</v>
       </c>
       <c r="S16" t="n">
-        <v>7.613399999999999</v>
+        <v>7.388</v>
       </c>
       <c r="T16" t="n">
-        <v>6.259900000000001</v>
+        <v>6.4703</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3535</v>
+        <v>0.9178999999999998</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8594999999999999</v>
+        <v>0.8899999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>10.0753</v>
+        <v>10.5254</v>
       </c>
       <c r="X16" t="n">
-        <v>-9.2157</v>
+        <v>-9.635499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_FUNDACIÓ CAIXA RURAL VILA-REAL.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_FUNDACIÓ CAIXA RURAL VILA-REAL.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>8.432499999999999</v>
+        <v>7.855</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8326</v>
+        <v>7.179600000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5999</v>
+        <v>0.6754</v>
       </c>
       <c r="G2" t="n">
         <v>4.0456</v>
@@ -610,13 +610,13 @@
         <v>3.3105</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6711</v>
+        <v>2.0936</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8492000000000002</v>
+        <v>1.1962</v>
       </c>
       <c r="U2" t="n">
-        <v>1.822</v>
+        <v>0.8975</v>
       </c>
       <c r="V2" t="n">
         <v>3.6632</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2869</v>
+        <v>5.0164</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2869</v>
+        <v>4.989100000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.02729999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2869</v>
+        <v>1.4556</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4632</v>
+        <v>2.4395</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8237</v>
+        <v>-0.984</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2869</v>
+        <v>3.1843</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4632</v>
+        <v>4.2618</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8237</v>
+        <v>-1.0775</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-1.7287</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-1.8223</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.09360000000000002</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1714</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.1942</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.9771</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8865</v>
+        <v>4.2869</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5424</v>
+        <v>4.2869</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6559</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4556</v>
+        <v>4.2869</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4395</v>
+        <v>2.4632</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.984</v>
+        <v>1.8237</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1843</v>
+        <v>4.2869</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2618</v>
+        <v>2.4632</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.0775</v>
+        <v>1.8237</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7287</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8223</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09360000000000002</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0415</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7475999999999999</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2939</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1202</v>
+        <v>3.7709</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8233</v>
+        <v>5.1463</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7031</v>
+        <v>-1.3754</v>
       </c>
       <c r="G5" t="n">
         <v>0.1286999999999998</v>
@@ -844,13 +844,13 @@
         <v>2.9211</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0509</v>
+        <v>1.7016</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4213</v>
+        <v>1.7444</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3703</v>
+        <v>-0.04269999999999996</v>
       </c>
       <c r="V5" t="n">
         <v>0.3826</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3149</v>
+        <v>1.4949</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1055999999999999</v>
+        <v>1.7893</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2093</v>
+        <v>-0.2945</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4808</v>
+        <v>0.8097</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3555</v>
+        <v>-1.1063</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1253</v>
+        <v>1.9161</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4372</v>
+        <v>1.3057</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9699</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4673</v>
+        <v>1.9292</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04350000000000001</v>
+        <v>-0.496</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6144000000000001</v>
+        <v>-0.4829</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6578999999999999</v>
+        <v>-0.0131</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9473</v>
+        <v>0.3895</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5038</v>
+        <v>0.8546</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2779</v>
+        <v>0.4836</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7817000000000001</v>
+        <v>0.371</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6621</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7639</v>
+        <v>1.1674</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1913</v>
+        <v>-0.0697000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4274</v>
+        <v>1.2372</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8097</v>
+        <v>2.4808</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1063</v>
+        <v>0.3555</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9161</v>
+        <v>2.1253</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3057</v>
+        <v>2.4372</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.9699</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9292</v>
+        <v>1.4673</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.496</v>
+        <v>0.04350000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4829</v>
+        <v>-0.6144000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0131</v>
+        <v>0.6578999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3895</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3895</v>
+        <v>1.9473</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1237</v>
+        <v>-0.6513</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1144</v>
+        <v>0.1025</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2381</v>
+        <v>-0.7538</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.6621</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. GARRIDO TALENS</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1515</v>
+        <v>0.2514999999999996</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.2152</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1515</v>
+        <v>-0.9635999999999998</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2658</v>
+        <v>4.1406</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.4366</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2658</v>
+        <v>3.704</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>4.4298</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.7628</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2658</v>
+        <v>-0.2892</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1.3262</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2658</v>
+        <v>1.037</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.9211</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.0631</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1144</v>
+        <v>1.143</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.348</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1144</v>
+        <v>0.7950999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.111</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.6116</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5922999999999999</v>
+        <v>0.1985000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2274</v>
+        <v>2.0739</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8197000000000001</v>
+        <v>-1.8754</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.7646</v>
+        <v>0.472</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.8539</v>
+        <v>-1.5513</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08940000000000003</v>
+        <v>2.0234</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0122</v>
+        <v>3.3232</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0646</v>
+        <v>1.3933</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9476</v>
+        <v>1.9298</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7524</v>
+        <v>-2.8511</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.7894</v>
+        <v>-2.9447</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0369</v>
+        <v>0.09350000000000003</v>
       </c>
       <c r="P9" t="n">
+        <v>-3.1158</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-5.0632</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.9474</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-0.1947</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.1421</v>
-      </c>
       <c r="S9" t="n">
-        <v>2.887</v>
+        <v>0.1206</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8754</v>
+        <v>0.4818</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0116</v>
+        <v>-0.3611</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6621</v>
+        <v>2.7216</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5590000000000001</v>
+        <v>3.3321</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2211</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MARIA VENTURA</t>
+          <t>M. GARRIDO TALENS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,61 +1186,61 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6269</v>
+        <v>0.1793</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.255</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.628</v>
+        <v>0.1793</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6003000000000001</v>
+        <v>0.2658</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7964</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1961</v>
+        <v>0.2658</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4156</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7108000000000001</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1264</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0159</v>
+        <v>0.2658</v>
       </c>
       <c r="N10" t="n">
-        <v>0.08560000000000001</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9303</v>
+        <v>0.2658</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1947</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1684</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.422</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8657</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5563</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>M. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7258</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1.366</v>
+        <v>-1.8941</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0918</v>
+        <v>1.9898</v>
       </c>
       <c r="G11" t="n">
-        <v>0.472</v>
+        <v>0.6003000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5513</v>
+        <v>0.7964</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0234</v>
+        <v>-0.1961</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3232</v>
+        <v>-0.4156</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3933</v>
+        <v>0.7108000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9298</v>
+        <v>-1.1264</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8511</v>
+        <v>1.0159</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.9447</v>
+        <v>0.08560000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09350000000000003</v>
+        <v>0.9303</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.1158</v>
+        <v>0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.0632</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9474</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8036</v>
+        <v>-0.6993</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.226</v>
+        <v>-0.5048</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5775</v>
+        <v>-0.1945</v>
       </c>
       <c r="V11" t="n">
-        <v>2.7216</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3321</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8726</v>
+        <v>-0.01930000000000009</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05690000000000001</v>
+        <v>0.9633999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9296</v>
+        <v>-0.9828</v>
       </c>
       <c r="G12" t="n">
-        <v>4.1406</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4366</v>
+        <v>-0.971</v>
       </c>
       <c r="I12" t="n">
-        <v>3.704</v>
+        <v>1.0526</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4298</v>
+        <v>0.9274000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7628</v>
+        <v>0.5132</v>
       </c>
       <c r="L12" t="n">
-        <v>2.667</v>
+        <v>0.4142</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2892</v>
+        <v>-0.8459000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3262</v>
+        <v>-1.4842</v>
       </c>
       <c r="O12" t="n">
-        <v>1.037</v>
+        <v>0.6382</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.9211</v>
+        <v>0.9736</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.0631</v>
+        <v>-0.1947</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1421</v>
+        <v>1.1684</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01889999999999997</v>
+        <v>-0.7951</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8103</v>
+        <v>0.2307</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8290999999999999</v>
+        <v>-1.0259</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.111</v>
+        <v>-0.2795</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5005</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.6116</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7125</v>
+        <v>-1.9152</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3185</v>
+        <v>-0.845</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.394</v>
+        <v>-1.0702</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08160000000000001</v>
+        <v>-4.7646</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.971</v>
+        <v>-4.8539</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0526</v>
+        <v>0.08940000000000003</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9274000000000001</v>
+        <v>-2.0122</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5132</v>
+        <v>-1.0646</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4142</v>
+        <v>-0.9476</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8459000000000001</v>
+        <v>-2.7524</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4842</v>
+        <v>-3.7894</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6382</v>
+        <v>1.0369</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9736</v>
+        <v>1.9474</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.1947</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1684</v>
+        <v>2.1421</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4882</v>
+        <v>1.5641</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0511</v>
+        <v>0.803</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.437</v>
+        <v>0.7611999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2795</v>
+        <v>-0.6621</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2795</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.5586</v>
+        <v>-4.414400000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.0121</v>
+        <v>-3.390899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5465</v>
+        <v>-1.0234</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.8782</v>
+        <v>-0.5457999999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.7793</v>
+        <v>-1.4921</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9011</v>
+        <v>0.9464000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.415</v>
+        <v>0.06450000000000022</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7978</v>
+        <v>0.01560000000000006</v>
       </c>
       <c r="L14" t="n">
-        <v>2.2129</v>
+        <v>0.04890000000000005</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2932</v>
+        <v>-0.6103</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.9816</v>
+        <v>-1.5078</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3117</v>
+        <v>0.8975</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.4263</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.789400000000001</v>
+        <v>-3.3105</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3631</v>
+        <v>1.1684</v>
       </c>
       <c r="S14" t="n">
-        <v>5.180099999999999</v>
+        <v>0.05349999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.7965</v>
+        <v>-0.1448</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3836</v>
+        <v>0.1984</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4342</v>
+        <v>-1.78</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.4342</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.7211</v>
+        <v>-5.6369</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.6761</v>
+        <v>-4.4182</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0451</v>
+        <v>-1.2188</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5457999999999998</v>
+        <v>-1.8782</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4921</v>
+        <v>-3.7793</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9464000000000001</v>
+        <v>1.9011</v>
       </c>
       <c r="J15" t="n">
-        <v>0.06450000000000022</v>
+        <v>1.415</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01560000000000006</v>
+        <v>-0.7978</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04890000000000005</v>
+        <v>2.2129</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6103</v>
+        <v>-3.2932</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5078</v>
+        <v>-2.9816</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8975</v>
+        <v>-0.3117</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.1421</v>
+        <v>-6.4263</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.3105</v>
+        <v>-7.789400000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1684</v>
+        <v>1.3631</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2532</v>
+        <v>3.1017</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4301</v>
+        <v>2.3903</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1768</v>
+        <v>0.7114</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.78</v>
+        <v>-0.4342</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.4342</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>9.146600000000005</v>
+        <v>12.3307</v>
       </c>
       <c r="E16" t="n">
-        <v>15.1707</v>
+        <v>17.02580000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.0244</v>
+        <v>-4.695099999999999</v>
       </c>
       <c r="G16" t="n">
         <v>11.579</v>
@@ -1690,28 +1690,28 @@
         <v>-24.0715</v>
       </c>
       <c r="O16" t="n">
-        <v>6.316999999999999</v>
+        <v>6.317</v>
       </c>
       <c r="P16" t="n">
         <v>-10.7107</v>
       </c>
       <c r="Q16" t="n">
-        <v>-31.1577</v>
+        <v>-31.15770000000001</v>
       </c>
       <c r="R16" t="n">
         <v>20.4472</v>
       </c>
       <c r="S16" t="n">
-        <v>7.388</v>
+        <v>10.5719</v>
       </c>
       <c r="T16" t="n">
-        <v>6.4703</v>
+        <v>8.325099999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9178999999999998</v>
+        <v>2.2472</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8899999999999999</v>
+        <v>0.8899999999999997</v>
       </c>
       <c r="W16" t="n">
         <v>10.5254</v>
